--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhhmjh.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhhmjh.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\JY-APS\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F76F22-8F72-4460-B5BF-86E005C27A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C091D6-937B-46E5-AFB2-74FAAD041919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1301,7 +1301,7 @@
       <c r="O5" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="P5" s="10" t="s">
+      <c r="P5" s="1" t="s">
         <v>47</v>
       </c>
     </row>

--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhhmjh.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhhmjh.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\JY-APS\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C091D6-937B-46E5-AFB2-74FAAD041919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D96F4F4E-FDD8-42D5-86C8-7770D3D37C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="硫化换模计划" sheetId="3" r:id="rId1"/>
@@ -651,7 +651,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -700,6 +700,9 @@
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1066,23 +1069,23 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:R5"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="11.4"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" style="14" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="9.88671875" style="15" customWidth="1" collapsed="1"/>
-    <col min="3" max="4" width="6.21875" style="6" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="5.21875" style="6" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="11.33203125" style="14" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="37.88671875" style="16" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="11.33203125" style="14" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="37.88671875" style="16" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="9.6640625" style="16" customWidth="1"/>
-    <col min="11" max="11" width="6.44140625" style="16" customWidth="1" collapsed="1"/>
-    <col min="12" max="14" width="6.44140625" style="6" customWidth="1" collapsed="1"/>
-    <col min="15" max="15" width="30.44140625" style="6" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="3.375" style="14" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="9.875" style="15" customWidth="1" collapsed="1"/>
+    <col min="3" max="4" width="6.25" style="6" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="5.25" style="6" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="11.375" style="14" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="37.875" style="16" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="11.375" style="14" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="37.875" style="16" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="9.625" style="16" customWidth="1"/>
+    <col min="11" max="11" width="6.5" style="16" customWidth="1" collapsed="1"/>
+    <col min="12" max="14" width="6.5" style="6" customWidth="1" collapsed="1"/>
+    <col min="15" max="15" width="30.5" style="6" customWidth="1" collapsed="1"/>
     <col min="16" max="16" width="10" style="6" customWidth="1" collapsed="1"/>
-    <col min="17" max="18" width="8.88671875" style="6"/>
-    <col min="19" max="16384" width="8.88671875" style="6" collapsed="1"/>
+    <col min="17" max="18" width="8.875" style="6"/>
+    <col min="19" max="16384" width="8.875" style="6" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" hidden="1">
@@ -1155,7 +1158,7 @@
       <c r="O2" s="4"/>
       <c r="P2" s="5"/>
     </row>
-    <row r="3" spans="1:16" s="8" customFormat="1" ht="34.200000000000003" customHeight="1">
+    <row r="3" spans="1:16" s="8" customFormat="1" ht="34.15" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>5</v>
       </c>
@@ -1255,7 +1258,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="11.4" customHeight="1">
+    <row r="5" spans="1:16" ht="11.45" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>32</v>
       </c>
@@ -1283,7 +1286,7 @@
       <c r="I5" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="17" t="s">
         <v>41</v>
       </c>
       <c r="K5" s="13" t="s">

--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhhmjh.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhhmjh.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\JY-APS\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D96F4F4E-FDD8-42D5-86C8-7770D3D37C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57863BD9-79A3-49AC-B3AB-B1272F7CB47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="硫化换模计划" sheetId="3" r:id="rId1"/>
@@ -1069,23 +1069,23 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:R5"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="11.4"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="14" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="9.875" style="15" customWidth="1" collapsed="1"/>
-    <col min="3" max="4" width="6.25" style="6" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="5.25" style="6" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="11.375" style="14" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="37.875" style="16" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="11.375" style="14" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="37.875" style="16" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="9.625" style="16" customWidth="1"/>
-    <col min="11" max="11" width="6.5" style="16" customWidth="1" collapsed="1"/>
-    <col min="12" max="14" width="6.5" style="6" customWidth="1" collapsed="1"/>
-    <col min="15" max="15" width="30.5" style="6" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="3.33203125" style="14" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="9.88671875" style="15" customWidth="1" collapsed="1"/>
+    <col min="3" max="4" width="6.21875" style="6" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="5.21875" style="6" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="11.33203125" style="14" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="37.88671875" style="16" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="11.33203125" style="14" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="37.88671875" style="16" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="9.6640625" style="16" customWidth="1"/>
+    <col min="11" max="11" width="6.44140625" style="16" customWidth="1" collapsed="1"/>
+    <col min="12" max="14" width="6.44140625" style="6" customWidth="1" collapsed="1"/>
+    <col min="15" max="15" width="30.44140625" style="6" customWidth="1" collapsed="1"/>
     <col min="16" max="16" width="10" style="6" customWidth="1" collapsed="1"/>
-    <col min="17" max="18" width="8.875" style="6"/>
-    <col min="19" max="16384" width="8.875" style="6" collapsed="1"/>
+    <col min="17" max="18" width="8.88671875" style="6"/>
+    <col min="19" max="16384" width="8.88671875" style="6" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" hidden="1">
@@ -1158,7 +1158,7 @@
       <c r="O2" s="4"/>
       <c r="P2" s="5"/>
     </row>
-    <row r="3" spans="1:16" s="8" customFormat="1" ht="34.15" customHeight="1">
+    <row r="3" spans="1:16" s="8" customFormat="1" ht="34.200000000000003" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>5</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="11.45" customHeight="1">
+    <row r="5" spans="1:16" ht="11.4" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>32</v>
       </c>
@@ -1304,7 +1304,7 @@
       <c r="O5" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="P5" s="10" t="s">
         <v>47</v>
       </c>
     </row>

--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhhmjh.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhhmjh.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\JY-APS\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57863BD9-79A3-49AC-B3AB-B1272F7CB47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C7AFA8-D0AD-4F74-8F7D-3D60D78B35AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="硫化换模计划" sheetId="3" r:id="rId1"/>
@@ -1071,19 +1071,18 @@
   <dimension ref="A1:R5"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="11.4"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" style="14" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="4.77734375" style="14" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="9.88671875" style="15" customWidth="1" collapsed="1"/>
     <col min="3" max="4" width="6.21875" style="6" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="5.21875" style="6" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="6.6640625" style="6" customWidth="1" collapsed="1"/>
     <col min="6" max="6" width="11.33203125" style="14" customWidth="1" collapsed="1"/>
     <col min="7" max="7" width="37.88671875" style="16" customWidth="1" collapsed="1"/>
     <col min="8" max="8" width="11.33203125" style="14" customWidth="1" collapsed="1"/>
     <col min="9" max="9" width="37.88671875" style="16" customWidth="1" collapsed="1"/>
     <col min="10" max="10" width="9.6640625" style="16" customWidth="1"/>
-    <col min="11" max="11" width="6.44140625" style="16" customWidth="1" collapsed="1"/>
-    <col min="12" max="14" width="6.44140625" style="6" customWidth="1" collapsed="1"/>
-    <col min="15" max="15" width="30.44140625" style="6" customWidth="1" collapsed="1"/>
-    <col min="16" max="16" width="10" style="6" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="6.77734375" style="16" customWidth="1" collapsed="1"/>
+    <col min="12" max="14" width="6.77734375" style="6" customWidth="1" collapsed="1"/>
+    <col min="15" max="16" width="30.44140625" style="6" customWidth="1" collapsed="1"/>
     <col min="17" max="18" width="8.88671875" style="6"/>
     <col min="19" max="16384" width="8.88671875" style="6" collapsed="1"/>
   </cols>

--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhhmjh.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhhmjh.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\JY-APS\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C7AFA8-D0AD-4F74-8F7D-3D60D78B35AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2056215E-305E-4470-A797-7CC29BD82325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8928" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="硫化换模计划" sheetId="3" r:id="rId1"/>
@@ -1080,7 +1080,7 @@
     <col min="8" max="8" width="11.33203125" style="14" customWidth="1" collapsed="1"/>
     <col min="9" max="9" width="37.88671875" style="16" customWidth="1" collapsed="1"/>
     <col min="10" max="10" width="9.6640625" style="16" customWidth="1"/>
-    <col min="11" max="11" width="6.77734375" style="16" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="25.5546875" style="16" customWidth="1" collapsed="1"/>
     <col min="12" max="14" width="6.77734375" style="6" customWidth="1" collapsed="1"/>
     <col min="15" max="16" width="30.44140625" style="6" customWidth="1" collapsed="1"/>
     <col min="17" max="18" width="8.88671875" style="6"/>
